--- a/data/indicateurs_regression_tous_cancers.xlsx
+++ b/data/indicateurs_regression_tous_cancers.xlsx
@@ -43,18 +43,18 @@
     <t>significativite</t>
   </si>
   <si>
+    <t>Poumon, bronche et trachée</t>
+  </si>
+  <si>
     <t>Leucémie aiguë myéloïde</t>
   </si>
   <si>
-    <t>Poumon, bronche et trachée</t>
+    <t>Sein</t>
   </si>
   <si>
     <t>Lymphome di us à grandes cellules B</t>
   </si>
   <si>
-    <t>Sein</t>
-  </si>
-  <si>
     <t>Myélome multiple et plasmocytome</t>
   </si>
   <si>
@@ -67,79 +67,79 @@
     <t>Prostate</t>
   </si>
   <si>
+    <t>Pancréas</t>
+  </si>
+  <si>
     <t>Colon rectum</t>
   </si>
   <si>
-    <t>Pancréas</t>
-  </si>
-  <si>
     <t>Syndrome myéloprolifératif chronique, autre que LMC</t>
   </si>
   <si>
     <t>Lèvre-cavité orale-pharynx</t>
   </si>
   <si>
+    <t>Larynx</t>
+  </si>
+  <si>
+    <t>Rein</t>
+  </si>
+  <si>
+    <t>Ovaire</t>
+  </si>
+  <si>
     <t>Estomac</t>
   </si>
   <si>
-    <t>Rein</t>
-  </si>
-  <si>
-    <t>Larynx</t>
+    <t>Lymphome de Hodgkin</t>
   </si>
   <si>
     <t>Corps de l'utérus</t>
   </si>
   <si>
+    <t>Mélanome de la peau</t>
+  </si>
+  <si>
+    <t>Leucémie myéloïde chronique (LMC)</t>
+  </si>
+  <si>
+    <t>Col de l'utérus</t>
+  </si>
+  <si>
+    <t>Lymphome T/NK à cellules matures</t>
+  </si>
+  <si>
     <t>OEsophage</t>
   </si>
   <si>
-    <t>Lymphome de Hodgkin</t>
-  </si>
-  <si>
-    <t>Mélanome de la peau</t>
-  </si>
-  <si>
-    <t>Col de l'utérus</t>
-  </si>
-  <si>
-    <t>Ovaire</t>
-  </si>
-  <si>
     <t>Testicule</t>
   </si>
   <si>
-    <t>Leucémie myéloïde chronique (LMC)</t>
-  </si>
-  <si>
-    <t>Lymphome T/NK à cellules matures</t>
-  </si>
-  <si>
     <t>Système nerveux central</t>
   </si>
   <si>
+    <t>Lymphome lympho-plasmocytaire / Macroglobulinémie de Waldenström</t>
+  </si>
+  <si>
+    <t>Lymphome de la zone marginale</t>
+  </si>
+  <si>
+    <t>Leucémie/lymphome lymphoblastique à cellules précurseurs (B, T ou SAI)</t>
+  </si>
+  <si>
+    <t>Lymphome folliculaire</t>
+  </si>
+  <si>
+    <t>Thyroïde</t>
+  </si>
+  <si>
+    <t>Foie</t>
+  </si>
+  <si>
+    <t>Lymphome à cellules du manteau</t>
+  </si>
+  <si>
     <t>Vessie</t>
-  </si>
-  <si>
-    <t>Leucémie/lymphome lymphoblastique à cellules précurseurs (B, T ou SAI)</t>
-  </si>
-  <si>
-    <t>Lymphome folliculaire</t>
-  </si>
-  <si>
-    <t>Lymphome lympho-plasmocytaire / Macroglobulinémie de Waldenström</t>
-  </si>
-  <si>
-    <t>Lymphome de la zone marginale</t>
-  </si>
-  <si>
-    <t>Thyroïde</t>
-  </si>
-  <si>
-    <t>Foie</t>
-  </si>
-  <si>
-    <t>Lymphome à cellules du manteau</t>
   </si>
   <si>
     <t>hausse significative</t>
@@ -546,22 +546,22 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>0.1396428571428572</v>
+        <v>0.4433823529411764</v>
       </c>
       <c r="E2">
-        <v>0.09757880575920511</v>
+        <v>0.2936163001362567</v>
       </c>
       <c r="F2">
-        <v>0.1817069085265092</v>
+        <v>0.5931484057460962</v>
       </c>
       <c r="G2">
-        <v>7.240406872785716E-06</v>
+        <v>1.799401273638492E-05</v>
       </c>
       <c r="H2">
-        <v>0.7982508354218882</v>
+        <v>0.7422582300641437</v>
       </c>
       <c r="I2" t="s">
         <v>42</v>
@@ -575,22 +575,22 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>0.4257142857142855</v>
+        <v>0.1225</v>
       </c>
       <c r="E3">
-        <v>0.2523803411420937</v>
+        <v>0.08111498455714941</v>
       </c>
       <c r="F3">
-        <v>0.5990482302864775</v>
+        <v>0.1638850154428506</v>
       </c>
       <c r="G3">
-        <v>0.0001423995584570338</v>
+        <v>1.802571269158107E-05</v>
       </c>
       <c r="H3">
-        <v>0.6841057851069885</v>
+        <v>0.7421947449768161</v>
       </c>
       <c r="I3" t="s">
         <v>42</v>
@@ -604,22 +604,22 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>0.06535714285714284</v>
+        <v>0.4008823529411762</v>
       </c>
       <c r="E4">
-        <v>0.01492074047458591</v>
+        <v>0.1518169405388756</v>
       </c>
       <c r="F4">
-        <v>0.1157935452396998</v>
+        <v>0.6499477653434769</v>
       </c>
       <c r="G4">
-        <v>0.01504479013243482</v>
+        <v>0.003888112926128048</v>
       </c>
       <c r="H4">
-        <v>0.3761118598382748</v>
+        <v>0.459818772245075</v>
       </c>
       <c r="I4" t="s">
         <v>42</v>
@@ -633,22 +633,22 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>0.3321428571428574</v>
+        <v>0.05176470588235295</v>
       </c>
       <c r="E5">
-        <v>0.05773284216689706</v>
+        <v>0.004323044565238771</v>
       </c>
       <c r="F5">
-        <v>0.6065528721188176</v>
+        <v>0.09920636719946713</v>
       </c>
       <c r="G5">
-        <v>0.02139287763838618</v>
+        <v>0.03460170056172423</v>
       </c>
       <c r="H5">
-        <v>0.3446798132164062</v>
+        <v>0.2811909949164851</v>
       </c>
       <c r="I5" t="s">
         <v>42</v>
@@ -662,25 +662,25 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>0.05285714285714287</v>
+        <v>0.03588235294117643</v>
       </c>
       <c r="E6">
-        <v>0.001491856661631888</v>
+        <v>-0.01615712468278873</v>
       </c>
       <c r="F6">
-        <v>0.1042224290526539</v>
+        <v>0.08792183056514161</v>
       </c>
       <c r="G6">
-        <v>0.04456256942338663</v>
+        <v>0.1613188174880752</v>
       </c>
       <c r="H6">
-        <v>0.2754527162977868</v>
+        <v>0.1351125635439358</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -691,22 +691,22 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>0.03928571428571428</v>
+        <v>0.02823529411764705</v>
       </c>
       <c r="E7">
-        <v>-0.01392053692213557</v>
+        <v>-0.02137221869568163</v>
       </c>
       <c r="F7">
-        <v>0.09249196549356412</v>
+        <v>0.07784280693097573</v>
       </c>
       <c r="G7">
-        <v>0.1346930597657053</v>
+        <v>0.2423405626380349</v>
       </c>
       <c r="H7">
-        <v>0.1636904761904762</v>
+        <v>0.09620543869721801</v>
       </c>
       <c r="I7" t="s">
         <v>43</v>
@@ -720,22 +720,22 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8">
-        <v>0.04428571428571427</v>
+        <v>0.03029411764705883</v>
       </c>
       <c r="E8">
-        <v>-0.02715225554436187</v>
+        <v>-0.03263694244397796</v>
       </c>
       <c r="F8">
-        <v>0.1157236841157904</v>
+        <v>0.0932251777380956</v>
       </c>
       <c r="G8">
-        <v>0.2034344410951586</v>
+        <v>0.3193591533031835</v>
       </c>
       <c r="H8">
-        <v>0.1212414315152024</v>
+        <v>0.07075496865412832</v>
       </c>
       <c r="I8" t="s">
         <v>43</v>
@@ -749,22 +749,22 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>-0.3496428571428571</v>
+        <v>-0.2292647058823526</v>
       </c>
       <c r="E9">
-        <v>-1.099819566982789</v>
+        <v>-0.8930955491657492</v>
       </c>
       <c r="F9">
-        <v>0.4005338526970752</v>
+        <v>0.434566137401044</v>
       </c>
       <c r="G9">
-        <v>0.3323547738206152</v>
+        <v>0.4710951401782227</v>
       </c>
       <c r="H9">
-        <v>0.0723469346059193</v>
+        <v>0.03771410837556893</v>
       </c>
       <c r="I9" t="s">
         <v>43</v>
@@ -778,25 +778,25 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>-0.5496428571428569</v>
+        <v>0.2311764705882353</v>
       </c>
       <c r="E10">
-        <v>-0.7670620245711884</v>
+        <v>0.1528576958537078</v>
       </c>
       <c r="F10">
-        <v>-0.3322236897145253</v>
+        <v>0.3094952453227627</v>
       </c>
       <c r="G10">
-        <v>0.0001090645904988216</v>
+        <v>1.856845833307285E-05</v>
       </c>
       <c r="H10">
-        <v>0.6964588583723694</v>
+        <v>0.7411224875389129</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -807,25 +807,25 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11">
-        <v>0.2321428571428571</v>
+        <v>-0.5144117647058823</v>
       </c>
       <c r="E11">
-        <v>0.1396780384946317</v>
+        <v>-0.7072256188682982</v>
       </c>
       <c r="F11">
-        <v>0.3246076757910825</v>
+        <v>-0.3215979105434665</v>
       </c>
       <c r="G11">
-        <v>0.0001163010777668555</v>
+        <v>5.276387658834086E-05</v>
       </c>
       <c r="H11">
-        <v>0.693526430059706</v>
+        <v>0.7004875245021711</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -836,22 +836,22 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12">
-        <v>0.1460714285714286</v>
+        <v>0.1601470588235294</v>
       </c>
       <c r="E12">
-        <v>0.06540446521673014</v>
+        <v>0.08902362099395911</v>
       </c>
       <c r="F12">
-        <v>0.226738391926127</v>
+        <v>0.2312704966530997</v>
       </c>
       <c r="G12">
-        <v>0.001785238046070514</v>
+        <v>0.0002674057710349794</v>
       </c>
       <c r="H12">
-        <v>0.5406951938492305</v>
+        <v>0.6248941534781155</v>
       </c>
       <c r="I12" t="s">
         <v>42</v>
@@ -865,22 +865,22 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13">
-        <v>-0.2157142857142856</v>
+        <v>-0.2176470588235294</v>
       </c>
       <c r="E13">
-        <v>-0.3501732202799904</v>
+        <v>-0.333095542533587</v>
       </c>
       <c r="F13">
-        <v>-0.08125535114858082</v>
+        <v>-0.1021985751134718</v>
       </c>
       <c r="G13">
-        <v>0.004178565919858128</v>
+        <v>0.001208724419691598</v>
       </c>
       <c r="H13">
-        <v>0.4802603402396982</v>
+        <v>0.5387033147567915</v>
       </c>
       <c r="I13" t="s">
         <v>44</v>
@@ -894,22 +894,22 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14">
-        <v>-0.1660714285714286</v>
+        <v>-0.09338235294117649</v>
       </c>
       <c r="E14">
-        <v>-0.2780626212362772</v>
+        <v>-0.1496361900445434</v>
       </c>
       <c r="F14">
-        <v>-0.05408023590658001</v>
+        <v>-0.0371285158378096</v>
       </c>
       <c r="G14">
-        <v>0.006919405534558107</v>
+        <v>0.003135603989013296</v>
       </c>
       <c r="H14">
-        <v>0.4411746702794465</v>
+        <v>0.4751901762407859</v>
       </c>
       <c r="I14" t="s">
         <v>44</v>
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15">
-        <v>0.1757142857142857</v>
+        <v>0.1739705882352941</v>
       </c>
       <c r="E15">
-        <v>0.04542688380046034</v>
+        <v>0.05975334748410001</v>
       </c>
       <c r="F15">
-        <v>0.3060016876281111</v>
+        <v>0.2881878289864883</v>
       </c>
       <c r="G15">
-        <v>0.01208774859589297</v>
+        <v>0.005621150032739473</v>
       </c>
       <c r="H15">
-        <v>0.3950439982244042</v>
+        <v>0.4325611872576581</v>
       </c>
       <c r="I15" t="s">
         <v>42</v>
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16">
-        <v>-0.08285714285714287</v>
+        <v>-0.08323529411764702</v>
       </c>
       <c r="E16">
-        <v>-0.1472220067530243</v>
+        <v>-0.1481615757616491</v>
       </c>
       <c r="F16">
-        <v>-0.0184922789612614</v>
+        <v>-0.01830901247364498</v>
       </c>
       <c r="G16">
-        <v>0.01558467839506715</v>
+        <v>0.01565696963163813</v>
       </c>
       <c r="H16">
-        <v>0.3730179264461282</v>
+        <v>0.3506600407189297</v>
       </c>
       <c r="I16" t="s">
         <v>44</v>
@@ -981,22 +981,22 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17">
-        <v>-0.1003571428571428</v>
+        <v>-0.1320588235294118</v>
       </c>
       <c r="E17">
-        <v>-0.1812010271418971</v>
+        <v>-0.2373339047226777</v>
       </c>
       <c r="F17">
-        <v>-0.01951325857238848</v>
+        <v>-0.0267837423361458</v>
       </c>
       <c r="G17">
-        <v>0.01883559876557445</v>
+        <v>0.01758211014561922</v>
       </c>
       <c r="H17">
-        <v>0.3561850430640425</v>
+        <v>0.3408214500054942</v>
       </c>
       <c r="I17" t="s">
         <v>44</v>
@@ -1010,25 +1010,25 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18">
-        <v>-0.05285714285714285</v>
+        <v>0.06058823529411764</v>
       </c>
       <c r="E18">
-        <v>-0.1059088237908749</v>
+        <v>0.007563192313924307</v>
       </c>
       <c r="F18">
-        <v>0.0001945380765891666</v>
+        <v>0.113613278274311</v>
       </c>
       <c r="G18">
-        <v>0.05072913333984408</v>
+        <v>0.02800571170250704</v>
       </c>
       <c r="H18">
-        <v>0.2627471051116371</v>
+        <v>0.3002086944218457</v>
       </c>
       <c r="I18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1039,25 +1039,25 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19">
-        <v>0.05892857142857141</v>
+        <v>-0.07720588235294115</v>
       </c>
       <c r="E19">
-        <v>-0.002102519656653305</v>
+        <v>-0.1530210165631044</v>
       </c>
       <c r="F19">
-        <v>0.1199596625137961</v>
+        <v>-0.001390748142777898</v>
       </c>
       <c r="G19">
-        <v>0.05725348732040204</v>
+        <v>0.04646064491716149</v>
       </c>
       <c r="H19">
-        <v>0.2507706573000587</v>
+        <v>0.2541458624362041</v>
       </c>
       <c r="I19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1068,25 +1068,25 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20">
-        <v>0.1460714285714285</v>
+        <v>0.1352941176470587</v>
       </c>
       <c r="E20">
-        <v>-0.006981847222037846</v>
+        <v>0.001235143151406104</v>
       </c>
       <c r="F20">
-        <v>0.2991247043648949</v>
+        <v>0.2693530921427114</v>
       </c>
       <c r="G20">
-        <v>0.05980735817798025</v>
+        <v>0.04819208257247044</v>
       </c>
       <c r="H20">
-        <v>0.2464247413203857</v>
+        <v>0.2507465516424133</v>
       </c>
       <c r="I20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1097,22 +1097,22 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>0.05178571428571428</v>
+        <v>0.03455882352941176</v>
       </c>
       <c r="E21">
-        <v>-0.004586672417494428</v>
+        <v>-3.4724964959848E-05</v>
       </c>
       <c r="F21">
-        <v>0.108158100988923</v>
+        <v>0.06915237202378337</v>
       </c>
       <c r="G21">
-        <v>0.06870800586862771</v>
+        <v>0.05020073580115639</v>
       </c>
       <c r="H21">
-        <v>0.2325225610475404</v>
+        <v>0.2469425626579023</v>
       </c>
       <c r="I21" t="s">
         <v>43</v>
@@ -1126,22 +1126,22 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22">
-        <v>-0.05999999999999998</v>
+        <v>0.04911764705882352</v>
       </c>
       <c r="E22">
-        <v>-0.1270667047460992</v>
+        <v>-0.0002045637692158972</v>
       </c>
       <c r="F22">
-        <v>0.00706670474609921</v>
+        <v>0.09843985788686294</v>
       </c>
       <c r="G22">
-        <v>0.07535138869792075</v>
+        <v>0.05083425453544735</v>
       </c>
       <c r="H22">
-        <v>0.2232063773250664</v>
+        <v>0.2457721965190569</v>
       </c>
       <c r="I22" t="s">
         <v>43</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23">
-        <v>0.07571428571428571</v>
+        <v>0.03205882352941177</v>
       </c>
       <c r="E23">
-        <v>-0.01025559767726271</v>
+        <v>-0.00182556096391788</v>
       </c>
       <c r="F23">
-        <v>0.1616841691058341</v>
+        <v>0.06594320802274142</v>
       </c>
       <c r="G23">
-        <v>0.0794687629798967</v>
+        <v>0.06189226530654092</v>
       </c>
       <c r="H23">
-        <v>0.2178138488976195</v>
+        <v>0.2272788139646103</v>
       </c>
       <c r="I23" t="s">
         <v>43</v>
@@ -1184,22 +1184,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24">
-        <v>0.03035714285714285</v>
+        <v>-0.04455882352941177</v>
       </c>
       <c r="E24">
-        <v>-0.007974966403011763</v>
+        <v>-0.09174893144335294</v>
       </c>
       <c r="F24">
-        <v>0.06868925211729747</v>
+        <v>0.002631284384529406</v>
       </c>
       <c r="G24">
-        <v>0.1108387989269667</v>
+        <v>0.06235155345818266</v>
       </c>
       <c r="H24">
-        <v>0.1837861212861213</v>
+        <v>0.2265797949135602</v>
       </c>
       <c r="I24" t="s">
         <v>43</v>
@@ -1213,22 +1213,22 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25">
-        <v>0.02642857142857143</v>
+        <v>0.06161764705882354</v>
       </c>
       <c r="E25">
-        <v>-0.01176610806845575</v>
+        <v>-0.01530956063323828</v>
       </c>
       <c r="F25">
-        <v>0.06462325092559859</v>
+        <v>0.1385448547508853</v>
       </c>
       <c r="G25">
-        <v>0.1588266393744298</v>
+        <v>0.1078334018315527</v>
       </c>
       <c r="H25">
-        <v>0.1466785714285714</v>
+        <v>0.1741063415166286</v>
       </c>
       <c r="I25" t="s">
         <v>43</v>
@@ -1242,22 +1242,22 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26">
-        <v>-0.03392857142857141</v>
+        <v>-0.02882352941176471</v>
       </c>
       <c r="E26">
-        <v>-0.09631029578563628</v>
+        <v>-0.08171761568031169</v>
       </c>
       <c r="F26">
-        <v>0.02845315292849346</v>
+        <v>0.02407055685678227</v>
       </c>
       <c r="G26">
-        <v>0.2610699199268671</v>
+        <v>0.2620182186849868</v>
       </c>
       <c r="H26">
-        <v>0.09600519119482577</v>
+        <v>0.0888971166751516</v>
       </c>
       <c r="I26" t="s">
         <v>43</v>
@@ -1271,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27">
-        <v>-0.02714285714285713</v>
+        <v>0.01911764705882353</v>
       </c>
       <c r="E27">
-        <v>-0.100156580629479</v>
+        <v>-0.01681099720767936</v>
       </c>
       <c r="F27">
-        <v>0.04587086634376472</v>
+        <v>0.05504629132532642</v>
       </c>
       <c r="G27">
-        <v>0.4363452374413064</v>
+        <v>0.2729151573871095</v>
       </c>
       <c r="H27">
-        <v>0.04726987036794554</v>
+        <v>0.08511281224818693</v>
       </c>
       <c r="I27" t="s">
         <v>43</v>
@@ -1300,22 +1300,22 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28">
-        <v>0.009642857142857144</v>
+        <v>-0.02794117647058824</v>
       </c>
       <c r="E28">
-        <v>-0.02300505734213143</v>
+        <v>-0.09585114407549057</v>
       </c>
       <c r="F28">
-        <v>0.04229077162784571</v>
+        <v>0.03996879113431411</v>
       </c>
       <c r="G28">
-        <v>0.5344977636757204</v>
+        <v>0.3924282269479455</v>
       </c>
       <c r="H28">
-        <v>0.03036825149966674</v>
+        <v>0.05269303751277187</v>
       </c>
       <c r="I28" t="s">
         <v>43</v>
@@ -1329,22 +1329,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29">
-        <v>0.02107142857142856</v>
+        <v>0.006764705882352938</v>
       </c>
       <c r="E29">
-        <v>-0.05294774422117639</v>
+        <v>-0.02308446245094956</v>
       </c>
       <c r="F29">
-        <v>0.09509060136403351</v>
+        <v>0.03661387421565544</v>
       </c>
       <c r="G29">
-        <v>0.5491668339248286</v>
+        <v>0.6344359425600585</v>
       </c>
       <c r="H29">
-        <v>0.02827200467815991</v>
+        <v>0.01659607843137253</v>
       </c>
       <c r="I29" t="s">
         <v>43</v>
@@ -1358,22 +1358,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D30">
-        <v>0.008928571428571423</v>
+        <v>0.01088235294117647</v>
       </c>
       <c r="E30">
-        <v>-0.03179917387950532</v>
+        <v>-0.05410190945079033</v>
       </c>
       <c r="F30">
-        <v>0.04965631673664817</v>
+        <v>0.07586661533314326</v>
       </c>
       <c r="G30">
-        <v>0.6436339081852686</v>
+        <v>0.7248280180169923</v>
       </c>
       <c r="H30">
-        <v>0.01696157186278765</v>
+        <v>0.00913031879418434</v>
       </c>
       <c r="I30" t="s">
         <v>43</v>
@@ -1387,22 +1387,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D31">
-        <v>-0.01678571428571429</v>
+        <v>-0.02117647058823525</v>
       </c>
       <c r="E31">
-        <v>-0.09342693271851814</v>
+        <v>-0.2172412259599343</v>
       </c>
       <c r="F31">
-        <v>0.05985550414708955</v>
+        <v>0.1748882847834638</v>
       </c>
       <c r="G31">
-        <v>0.6439474239961636</v>
+        <v>0.8201591108155525</v>
       </c>
       <c r="H31">
-        <v>0.01692979767014103</v>
+        <v>0.003818446988111532</v>
       </c>
       <c r="I31" t="s">
         <v>43</v>
@@ -1416,22 +1416,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D32">
-        <v>0.03892857142857149</v>
+        <v>-0.008088235294117643</v>
       </c>
       <c r="E32">
-        <v>-0.1704443199795306</v>
+        <v>-0.0913421716633732</v>
       </c>
       <c r="F32">
-        <v>0.2483014628366735</v>
+        <v>0.07516570107513791</v>
       </c>
       <c r="G32">
-        <v>0.6944477852826731</v>
+        <v>0.8379418635964502</v>
       </c>
       <c r="H32">
-        <v>0.01225890105657059</v>
+        <v>0.003091671904623193</v>
       </c>
       <c r="I32" t="s">
         <v>43</v>
@@ -1445,22 +1445,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D33">
-        <v>0.00178571428571426</v>
+        <v>0.0008823529411764671</v>
       </c>
       <c r="E33">
-        <v>-0.09142760855183918</v>
+        <v>-0.02319232205178538</v>
       </c>
       <c r="F33">
-        <v>0.09499903712326771</v>
+        <v>0.02495702793413831</v>
       </c>
       <c r="G33">
-        <v>0.9676164260114615</v>
+        <v>0.9384570329644317</v>
       </c>
       <c r="H33">
-        <v>0.0001317416598746484</v>
+        <v>0.0004411764705882317</v>
       </c>
       <c r="I33" t="s">
         <v>43</v>
@@ -1474,22 +1474,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D34">
-        <v>-0.0003571428571428567</v>
+        <v>0.002058823529411789</v>
       </c>
       <c r="E34">
-        <v>-0.02803118307076251</v>
+        <v>-0.06990340934417498</v>
       </c>
       <c r="F34">
-        <v>0.02731689735647679</v>
+        <v>0.07402105640299857</v>
       </c>
       <c r="G34">
-        <v>0.9781810872738457</v>
+        <v>0.951938419248799</v>
       </c>
       <c r="H34">
-        <v>5.978954081632637E-05</v>
+        <v>0.000268876207199304</v>
       </c>
       <c r="I34" t="s">
         <v>43</v>
